--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9950-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9950-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEAA4D43-011E-41A9-BEC9-672EA1705809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9C7377D-7E2B-4EFE-98BC-565BD01F3682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4173666E-9B2A-4398-9F9D-D83AAD0FB709}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1FEE9623-5446-410C-9A97-B235F93FFCD8}"/>
   </bookViews>
   <sheets>
     <sheet name="9950-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1457,29 +1457,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7DB48E-C7C4-49B5-AC97-134523A52EF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491B322E-2BAA-47CA-B6D7-5A5CAFDF3924}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1513,7 +1512,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1549,7 +1548,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1601,7 +1600,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1669,7 +1668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1813,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1885,7 +1884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2029,7 +2028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2101,7 +2100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2173,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2245,7 +2244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2317,7 +2316,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2389,7 +2388,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2461,7 +2460,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2533,7 +2532,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2605,7 +2604,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2749,7 +2748,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2821,7 +2820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2965,7 +2964,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3037,7 +3036,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3181,7 +3180,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3253,7 +3252,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3325,7 +3324,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3397,7 +3396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>1999</v>
       </c>
@@ -3469,7 +3468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36" t="s">
         <v>44</v>
       </c>
